--- a/GEMINI_APIs/apikeys.xlsx
+++ b/GEMINI_APIs/apikeys.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IDP_2.0-INVOICE\GEMINI_APIs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{953A2420-D30A-4074-BED3-C00327B86F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B603348-E722-42C1-9652-00B28D3BBC10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -486,6 +486,9 @@
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="B8" s="3">
+        <v>46203</v>
+      </c>
       <c r="C8" t="s">
         <v>13</v>
       </c>
@@ -494,6 +497,9 @@
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="B9" s="3">
+        <v>46203</v>
+      </c>
       <c r="C9" t="s">
         <v>14</v>
       </c>
@@ -501,6 +507,9 @@
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>11</v>
+      </c>
+      <c r="B10" s="3">
+        <v>46202</v>
       </c>
       <c r="C10" t="s">
         <v>15</v>
